--- a/SMT/A2Pico2Lite-SMD.v1.0_BOM.xlsx
+++ b/SMT/A2Pico2Lite-SMD.v1.0_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2Lite-SMD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA98CCD-FD76-40BC-A2F8-ABF51B837908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC49EC26-1E7B-4514-B5E8-0A70E5B1FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>FU1</t>
   </si>
   <si>
-    <t>White LED A13150060VS75000</t>
-  </si>
-  <si>
     <t>1k</t>
   </si>
   <si>
@@ -167,24 +164,9 @@
     <t>C25190</t>
   </si>
   <si>
-    <t>C20625731</t>
-  </si>
-  <si>
-    <t>ABM8-272-T3</t>
-  </si>
-  <si>
-    <t>C42411119</t>
-  </si>
-  <si>
-    <t>12pF</t>
-  </si>
-  <si>
     <t>LED1</t>
   </si>
   <si>
-    <t>C1547</t>
-  </si>
-  <si>
     <t>C19702</t>
   </si>
   <si>
@@ -245,9 +227,6 @@
     <t>C720477</t>
   </si>
   <si>
-    <t>C2290</t>
-  </si>
-  <si>
     <t>C4109</t>
   </si>
   <si>
@@ -261,6 +240,27 @@
   </si>
   <si>
     <t>R12</t>
+  </si>
+  <si>
+    <t>C48783272</t>
+  </si>
+  <si>
+    <t>C397049</t>
+  </si>
+  <si>
+    <t>White LED</t>
+  </si>
+  <si>
+    <t>C403945</t>
+  </si>
+  <si>
+    <t>12MHz</t>
+  </si>
+  <si>
+    <t>C1549</t>
+  </si>
+  <si>
+    <t>18pF</t>
   </si>
 </sst>
 </file>
@@ -770,52 +770,52 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -826,16 +826,16 @@
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1">
@@ -849,44 +849,44 @@
         <v>10</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>61</v>
@@ -895,46 +895,46 @@
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" ht="20" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E12" s="12"/>
     </row>
     <row r="13" spans="1:5" ht="20" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20" customHeight="1">
@@ -942,27 +942,27 @@
         <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
@@ -970,64 +970,64 @@
         <v>27</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1">
       <c r="A19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/SMT/A2Pico2Lite-SMD.v1.0_BOM.xlsx
+++ b/SMT/A2Pico2Lite-SMD.v1.0_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2Lite-SMD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC49EC26-1E7B-4514-B5E8-0A70E5B1FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872AF226-C30F-4224-B475-6F354DAD5587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,9 +176,6 @@
     <t>6.3V 10uF 0603</t>
   </si>
   <si>
-    <t>6.3V 4.7uF 0603</t>
-  </si>
-  <si>
     <t>16V 100nF 0402</t>
   </si>
   <si>
@@ -233,12 +230,6 @@
     <t>C11702</t>
   </si>
   <si>
-    <t>R2,R4,R5,R7</t>
-  </si>
-  <si>
-    <t>R1,R3,R6,R8,R9,R13</t>
-  </si>
-  <si>
     <t>R12</t>
   </si>
   <si>
@@ -261,6 +252,15 @@
   </si>
   <si>
     <t>18pF</t>
+  </si>
+  <si>
+    <t>6.3V 4.7uF</t>
+  </si>
+  <si>
+    <t>R2,R4,R7</t>
+  </si>
+  <si>
+    <t>R1,R3,R5,R6,R8,R9,R13</t>
   </si>
 </sst>
 </file>
@@ -770,24 +770,24 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>24</v>
@@ -801,7 +801,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>24</v>
@@ -812,10 +812,10 @@
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -860,7 +860,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
@@ -875,12 +875,12 @@
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>34</v>
@@ -889,7 +889,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -898,28 +898,28 @@
         <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" ht="20" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -928,7 +928,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -942,7 +942,7 @@
         <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -956,7 +956,7 @@
         <v>29</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -970,7 +970,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
@@ -981,28 +981,28 @@
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>28</v>
@@ -1027,7 +1027,7 @@
         <v>16</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
